--- a/artfynd/A 21809-2024 artfynd.xlsx
+++ b/artfynd/A 21809-2024 artfynd.xlsx
@@ -1197,10 +1197,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121158821</v>
+        <v>121158826</v>
       </c>
       <c r="B6" t="n">
-        <v>100337</v>
+        <v>100347</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1241,10 +1241,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650842</v>
+        <v>650779</v>
       </c>
       <c r="R6" t="n">
-        <v>6633410</v>
+        <v>6633164</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Viktor Bolin</t>
+          <t>Anna Broberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1311,7 +1311,7 @@
         <v>121158827</v>
       </c>
       <c r="B7" t="n">
-        <v>100337</v>
+        <v>100347</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1419,10 +1419,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121158826</v>
+        <v>121158821</v>
       </c>
       <c r="B8" t="n">
-        <v>100337</v>
+        <v>100347</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650779</v>
+        <v>650842</v>
       </c>
       <c r="R8" t="n">
-        <v>6633164</v>
+        <v>6633410</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1493,12 +1493,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anna Broberg</t>
+          <t>Viktor Bolin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 21809-2024 artfynd.xlsx
+++ b/artfynd/A 21809-2024 artfynd.xlsx
@@ -1197,7 +1197,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121158826</v>
+        <v>121158821</v>
       </c>
       <c r="B6" t="n">
         <v>100347</v>
@@ -1241,10 +1241,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650779</v>
+        <v>650842</v>
       </c>
       <c r="R6" t="n">
-        <v>6633164</v>
+        <v>6633410</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna Broberg</t>
+          <t>Viktor Bolin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1308,7 +1308,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121158827</v>
+        <v>121158826</v>
       </c>
       <c r="B7" t="n">
         <v>100347</v>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650799</v>
+        <v>650779</v>
       </c>
       <c r="R7" t="n">
-        <v>6633128</v>
+        <v>6633164</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Max Ljungkvist</t>
+          <t>Anna Broberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1419,7 +1419,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121158821</v>
+        <v>121158827</v>
       </c>
       <c r="B8" t="n">
         <v>100347</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650842</v>
+        <v>650799</v>
       </c>
       <c r="R8" t="n">
-        <v>6633410</v>
+        <v>6633128</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1493,12 +1493,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Viktor Bolin</t>
+          <t>Max Ljungkvist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 21809-2024 artfynd.xlsx
+++ b/artfynd/A 21809-2024 artfynd.xlsx
@@ -1197,10 +1197,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121158821</v>
+        <v>121158826</v>
       </c>
       <c r="B6" t="n">
-        <v>100347</v>
+        <v>100360</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1241,10 +1241,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650842</v>
+        <v>650779</v>
       </c>
       <c r="R6" t="n">
-        <v>6633410</v>
+        <v>6633164</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Viktor Bolin</t>
+          <t>Anna Broberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1308,10 +1308,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121158826</v>
+        <v>121158821</v>
       </c>
       <c r="B7" t="n">
-        <v>100347</v>
+        <v>100360</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650779</v>
+        <v>650842</v>
       </c>
       <c r="R7" t="n">
-        <v>6633164</v>
+        <v>6633410</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1382,12 +1382,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anna Broberg</t>
+          <t>Viktor Bolin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1422,7 +1422,7 @@
         <v>121158827</v>
       </c>
       <c r="B8" t="n">
-        <v>100347</v>
+        <v>100360</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 21809-2024 artfynd.xlsx
+++ b/artfynd/A 21809-2024 artfynd.xlsx
@@ -1200,7 +1200,7 @@
         <v>121158826</v>
       </c>
       <c r="B6" t="n">
-        <v>100360</v>
+        <v>100361</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1308,10 +1308,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121158821</v>
+        <v>121158827</v>
       </c>
       <c r="B7" t="n">
-        <v>100360</v>
+        <v>100361</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650842</v>
+        <v>650799</v>
       </c>
       <c r="R7" t="n">
-        <v>6633410</v>
+        <v>6633128</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1382,12 +1382,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Viktor Bolin</t>
+          <t>Max Ljungkvist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1419,10 +1419,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121158827</v>
+        <v>121158821</v>
       </c>
       <c r="B8" t="n">
-        <v>100360</v>
+        <v>100361</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650799</v>
+        <v>650842</v>
       </c>
       <c r="R8" t="n">
-        <v>6633128</v>
+        <v>6633410</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1493,12 +1493,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Max Ljungkvist</t>
+          <t>Viktor Bolin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 21809-2024 artfynd.xlsx
+++ b/artfynd/A 21809-2024 artfynd.xlsx
@@ -1197,10 +1197,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121158826</v>
+        <v>121158827</v>
       </c>
       <c r="B6" t="n">
-        <v>100361</v>
+        <v>100364</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1241,10 +1241,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650779</v>
+        <v>650799</v>
       </c>
       <c r="R6" t="n">
-        <v>6633164</v>
+        <v>6633128</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna Broberg</t>
+          <t>Max Ljungkvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1308,10 +1308,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121158827</v>
+        <v>121158826</v>
       </c>
       <c r="B7" t="n">
-        <v>100361</v>
+        <v>100364</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650799</v>
+        <v>650779</v>
       </c>
       <c r="R7" t="n">
-        <v>6633128</v>
+        <v>6633164</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Max Ljungkvist</t>
+          <t>Anna Broberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1422,7 +1422,7 @@
         <v>121158821</v>
       </c>
       <c r="B8" t="n">
-        <v>100361</v>
+        <v>100364</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 21809-2024 artfynd.xlsx
+++ b/artfynd/A 21809-2024 artfynd.xlsx
@@ -1197,7 +1197,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121158827</v>
+        <v>121158821</v>
       </c>
       <c r="B6" t="n">
         <v>100364</v>
@@ -1241,10 +1241,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650799</v>
+        <v>650842</v>
       </c>
       <c r="R6" t="n">
-        <v>6633128</v>
+        <v>6633410</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Max Ljungkvist</t>
+          <t>Viktor Bolin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1308,7 +1308,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121158826</v>
+        <v>121158827</v>
       </c>
       <c r="B7" t="n">
         <v>100364</v>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650779</v>
+        <v>650799</v>
       </c>
       <c r="R7" t="n">
-        <v>6633164</v>
+        <v>6633128</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anna Broberg</t>
+          <t>Max Ljungkvist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1419,7 +1419,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121158821</v>
+        <v>121158826</v>
       </c>
       <c r="B8" t="n">
         <v>100364</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650842</v>
+        <v>650779</v>
       </c>
       <c r="R8" t="n">
-        <v>6633410</v>
+        <v>6633164</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1493,12 +1493,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Viktor Bolin</t>
+          <t>Anna Broberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 21809-2024 artfynd.xlsx
+++ b/artfynd/A 21809-2024 artfynd.xlsx
@@ -1197,10 +1197,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121158821</v>
+        <v>121158827</v>
       </c>
       <c r="B6" t="n">
-        <v>100364</v>
+        <v>100370</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1241,10 +1241,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650842</v>
+        <v>650799</v>
       </c>
       <c r="R6" t="n">
-        <v>6633410</v>
+        <v>6633128</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Viktor Bolin</t>
+          <t>Max Ljungkvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1308,10 +1308,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121158827</v>
+        <v>121158821</v>
       </c>
       <c r="B7" t="n">
-        <v>100364</v>
+        <v>100370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650799</v>
+        <v>650842</v>
       </c>
       <c r="R7" t="n">
-        <v>6633128</v>
+        <v>6633410</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1382,12 +1382,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Max Ljungkvist</t>
+          <t>Viktor Bolin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1422,7 +1422,7 @@
         <v>121158826</v>
       </c>
       <c r="B8" t="n">
-        <v>100364</v>
+        <v>100370</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 21809-2024 artfynd.xlsx
+++ b/artfynd/A 21809-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1528,6 +1528,126 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127884276</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56585</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100053</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Igelkott</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Erinaceus europaeus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Stenbrohultsvägen, 757 54 Uppsala, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>651089</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6633048</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Danmark</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Johan Möller</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Johan Möller</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>WWF - Tillsammans för Sveriges igelkottar</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21809-2024 artfynd.xlsx
+++ b/artfynd/A 21809-2024 artfynd.xlsx
@@ -1533,7 +1533,7 @@
         <v>127884276</v>
       </c>
       <c r="B9" t="n">
-        <v>56585</v>
+        <v>56612</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 21809-2024 artfynd.xlsx
+++ b/artfynd/A 21809-2024 artfynd.xlsx
@@ -1533,7 +1533,7 @@
         <v>127884276</v>
       </c>
       <c r="B9" t="n">
-        <v>56612</v>
+        <v>56615</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 21809-2024 artfynd.xlsx
+++ b/artfynd/A 21809-2024 artfynd.xlsx
@@ -1533,7 +1533,7 @@
         <v>127884276</v>
       </c>
       <c r="B9" t="n">
-        <v>56615</v>
+        <v>56618</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 21809-2024 artfynd.xlsx
+++ b/artfynd/A 21809-2024 artfynd.xlsx
@@ -1533,7 +1533,7 @@
         <v>127884276</v>
       </c>
       <c r="B9" t="n">
-        <v>56618</v>
+        <v>56620</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 21809-2024 artfynd.xlsx
+++ b/artfynd/A 21809-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97505912</v>
+        <v>76111686</v>
       </c>
       <c r="B2" t="n">
-        <v>57484</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,56 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205998</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>detektor med höghastighetsinspelning</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Uppsala, Upl</t>
+          <t>Sydöstra Staden, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650759.7692892307</v>
+        <v>650890</v>
       </c>
       <c r="R2" t="n">
-        <v>6633099.946233045</v>
+        <v>6633033</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-07-22</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>23:55</t>
+          <t>2018-08-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-07-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>23:55</t>
+          <t>2018-10-31</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Fynden gjordes mellan augusti och oktober 2018.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,49 +765,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Martin Brüsin</t>
+          <t>Magnus Stenmark</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johanna Kammonen, Emily Macgregor</t>
+          <t>Sofia Lundell, Karin Agstam-Norlin, Cecilia Rätz</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97505915</v>
+        <v>127884276</v>
       </c>
       <c r="B3" t="n">
-        <v>57503</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56845</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205995</v>
+        <v>100053</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Erinaceus europaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -844,34 +810,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>detektor med höghastighetsinspelning</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Uppsala, Upl</t>
+          <t>Stenbrohultsvägen, 757 54 Uppsala, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650865.6790536554</v>
+        <v>651089</v>
       </c>
       <c r="R3" t="n">
-        <v>6633113.311064495</v>
+        <v>6633048</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -895,22 +851,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-07-22</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>23:53</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-07-23</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>23:53</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,86 +881,68 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Martin Brüsin</t>
+          <t>Johan Möller</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johanna Kammonen, Emily Macgregor</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Via Johan Möller</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>WWF - Tillsammans för Sveriges igelkottar</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>100060756</v>
+        <v>106286109</v>
       </c>
       <c r="B4" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>6675</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>100763</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Cinnoberbagge</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Cucujus cinnaberinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stenbrohultsvägen, Sävja, Upl</t>
+          <t>Uppsala, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>651046.8728644639</v>
+        <v>650735</v>
       </c>
       <c r="R4" t="n">
-        <v>6633173.556520145</v>
+        <v>6633096</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1028,27 +966,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-04-19</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-04-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:25</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På timmertravar.</t>
+          <t>larv</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1057,80 +985,91 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Owe Rosengren</t>
+          <t>Alexander Schäpers</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Owe Rosengren, Åke Berg, Niklas Hjort, Patrick Fritzson</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>100060686</v>
+        <v>110455844</v>
       </c>
       <c r="B5" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>102018</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Zygaena lonicerae</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Scheven, 1777)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stenbrohultsvägen, Sävja, Upl</t>
+          <t>Skåneresan, Uppsala, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>651046.8728644639</v>
+        <v>650976</v>
       </c>
       <c r="R5" t="n">
-        <v>6633173.556520145</v>
+        <v>6633092</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1154,22 +1093,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-04-19</t>
+          <t>2023-06-30</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-04-19</t>
+          <t>2023-06-30</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1178,76 +1117,78 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Owe Rosengren</t>
+          <t>Fredrik Thunarf</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Owe Rosengren, Åke Berg, Niklas Hjort, Patrick Fritzson</t>
+          <t>Fredrik Thunarf</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121158827</v>
+        <v>133560128</v>
       </c>
       <c r="B6" t="n">
-        <v>100370</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57259</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>102972</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Turkduva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Streptopelia decaocto</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Frivaldszky, 1838)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sävja, Upl</t>
+          <t>Infarten Sävja södra, Sävja, Uppsala, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650799</v>
+        <v>651100</v>
       </c>
       <c r="R6" t="n">
-        <v>6633128</v>
+        <v>6633043</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1271,12 +1212,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,80 +1236,81 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kirsi Jokinen</t>
+          <t>Samuel Öhlin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Max Ljungkvist</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering vid Sweco</t>
-        </is>
-      </c>
+          <t>Samuel Öhlin</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121158821</v>
+        <v>100162359</v>
       </c>
       <c r="B7" t="n">
-        <v>100370</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>102990</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sävja, Upl</t>
+          <t>Trave Sävja, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650842</v>
+        <v>651066</v>
       </c>
       <c r="R7" t="n">
-        <v>6633410</v>
+        <v>6633159</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1382,12 +1334,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2022-04-23</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2022-04-23</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1396,38 +1358,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kirsi Jokinen</t>
+          <t>Joakim Djerf</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Viktor Bolin</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering vid Sweco</t>
-        </is>
-      </c>
+          <t>Joakim Djerf</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121158826</v>
+        <v>100060756</v>
       </c>
       <c r="B8" t="n">
-        <v>100370</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1435,41 +1387,58 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sävja, Upl</t>
+          <t>Stenbrohultsvägen, Sävja, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650779</v>
+        <v>651047</v>
       </c>
       <c r="R8" t="n">
-        <v>6633164</v>
+        <v>6633174</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1493,12 +1462,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2022-04-19</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2022-04-19</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På timmertravar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1514,26 +1498,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kirsi Jokinen</t>
+          <t>Owe Rosengren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anna Broberg</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering vid Sweco</t>
-        </is>
-      </c>
+          <t>Owe Rosengren, Åke Berg, Niklas Hjort, Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127884276</v>
+        <v>111203552</v>
       </c>
       <c r="B9" t="n">
-        <v>56620</v>
+        <v>43219</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1541,21 +1521,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100053</v>
+        <v>201028</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Mindre tåtelsmygare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Erinaceus europaeus</t>
+          <t>Thymelicus lineola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ochsenheimer, 1808)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1563,6 +1543,22 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1570,17 +1566,17 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stenbrohultsvägen, 757 54 Uppsala, Upl</t>
+          <t>Sävja, Uppsala, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>651089</v>
+        <v>651045</v>
       </c>
       <c r="R9" t="n">
-        <v>6633048</v>
+        <v>6633023</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1604,22 +1600,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1634,17 +1630,1541 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Johan Möller</t>
+          <t>Fredrik Thunarf</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Johan Möller</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>WWF - Tillsammans för Sveriges igelkottar</t>
+          <t>Fredrik Thunarf</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>97505950</v>
+      </c>
+      <c r="B10" t="n">
+        <v>56823</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Uppsala, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>650958</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6633231</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Danmark</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2021-07-19</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2021-07-24</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Johanna Kammonen, Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>97505915</v>
+      </c>
+      <c r="B11" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Uppsala, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>650865</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6633114</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Danmark</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-07-22</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>23:53</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-07-23</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>23:53</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Johanna Kammonen, Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>97505948</v>
+      </c>
+      <c r="B12" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Uppsala, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>650958</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6633231</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Danmark</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-07-19</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-07-24</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Johanna Kammonen, Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>97506021</v>
+      </c>
+      <c r="B13" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Uppsala, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>650964</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6633407</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Danmark</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2021-07-23</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>00:12</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2021-07-24</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>00:12</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Johanna Kammonen, Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>97505910</v>
+      </c>
+      <c r="B14" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Uppsala, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>650760</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6633100</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Danmark</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2021-07-22</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>23:55</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2021-07-23</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>23:55</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Johanna Kammonen, Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>97505951</v>
+      </c>
+      <c r="B15" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Uppsala, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>650958</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6633231</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Danmark</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2021-07-19</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2021-07-24</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Johanna Kammonen, Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>97505946</v>
+      </c>
+      <c r="B16" t="n">
+        <v>56837</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Uppsala, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>650958</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6633231</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Danmark</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2021-07-19</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2021-07-24</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Johanna Kammonen, Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>100060686</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Stenbrohultsvägen, Sävja, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>651047</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6633174</v>
+      </c>
+      <c r="S17" t="n">
+        <v>50</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Danmark</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2022-04-19</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2022-04-19</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Owe Rosengren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Owe Rosengren, Åke Berg, Niklas Hjort, Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>121158821</v>
+      </c>
+      <c r="B18" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Sävja, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>650842</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6633410</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Danmark</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Kirsi Jokinen</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Viktor Bolin</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering vid Sweco</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>121158825</v>
+      </c>
+      <c r="B19" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sävja, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>650753</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6633137</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Danmark</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Kirsi Jokinen</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anna Broberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering vid Sweco</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>121158826</v>
+      </c>
+      <c r="B20" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Sävja, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>650779</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6633164</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Danmark</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kirsi Jokinen</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anna Broberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering vid Sweco</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>121158827</v>
+      </c>
+      <c r="B21" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Sävja, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>650799</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6633128</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Danmark</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kirsi Jokinen</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Max Ljungkvist</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering vid Sweco</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>121158828</v>
+      </c>
+      <c r="B22" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Sävja, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>650956</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6633228</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Danmark</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Kirsi Jokinen</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anna Broberg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering vid Sweco</t>
         </is>
       </c>
     </row>
